--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203169</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136203177</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203169</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136203177</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203169</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136203177</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203169</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136203177</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136203169</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136203177</v>
       </c>
       <c r="B5" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32590-2026 artfynd.xlsx
+++ b/artfynd/A 32590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136203174</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136203170</v>
       </c>
       <c r="B3" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
